--- a/data/raw/sales_january.xlsx
+++ b/data/raw/sales_january.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Widget B</t>
+          <t xml:space="preserve">  widget b  </t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -496,7 +496,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>SOUTH</t>
         </is>
       </c>
     </row>
@@ -523,6 +523,58 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>East</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-01-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Widget A</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NOT A DATE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Widget C</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>West</t>
         </is>
       </c>
     </row>
